--- a/shop/dist/06-3-Statement-Financial-Model-Template.xlsx
+++ b/shop/dist/06-3-Statement-Financial-Model-Template.xlsx
@@ -1829,23 +1829,23 @@
         <v/>
       </c>
       <c r="C17" s="25">
-        <f>-C15*Assumptions!C$13</f>
+        <f>-MAX(0,C15)*Assumptions!C$13</f>
         <v/>
       </c>
       <c r="D17" s="25">
-        <f>-D15*Assumptions!D$13</f>
+        <f>-MAX(0,D15)*Assumptions!D$13</f>
         <v/>
       </c>
       <c r="E17" s="25">
-        <f>-E15*Assumptions!E$13</f>
+        <f>-MAX(0,E15)*Assumptions!E$13</f>
         <v/>
       </c>
       <c r="F17" s="25">
-        <f>-F15*Assumptions!F$13</f>
+        <f>-MAX(0,F15)*Assumptions!F$13</f>
         <v/>
       </c>
       <c r="G17" s="25">
-        <f>-G15*Assumptions!G$13</f>
+        <f>-MAX(0,G15)*Assumptions!G$13</f>
         <v/>
       </c>
     </row>
